--- a/ig/main/CodeSystem-terminologie-catalogue-vaccins.xlsx
+++ b/ig/main/CodeSystem-terminologie-catalogue-vaccins.xlsx
@@ -31,7 +31,7 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/#terminologie-catalogue-vaccins (use: secondary, )</t>
+    <t>https://smt.esante.gouv.fr/#terminologie-catalogue-vaccins (use: secondary)</t>
   </si>
   <si>
     <t>Version</t>
